--- a/3학년 2학기/기인프/기인프 5반 좌석표 개선판.xlsx
+++ b/3학년 2학기/기인프/기인프 5반 좌석표 개선판.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\SOGANG\3학년 2학기\기인프\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79144A3-F060-4542-9FD3-A02214147EEB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E015F87-784C-4F0A-AEDF-5A7B77C37F7A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9564" xr2:uid="{127D69E5-7973-4135-B76A-078775FF16D0}"/>
   </bookViews>
@@ -25,19 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>교탁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hy** **an
-2026***1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>JU **XUN
-2025*0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -56,8 +46,248 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>박*몽
+    <t>김*규
+2026***6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김*유
+2023***9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>임*준
+2024***3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이*현
+2022***0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안*율
+2026***3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박*현
+2026***9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김*현
+2026***8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>권*원
+2026***2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김*빈
+2023***7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍*현
+2025***7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이*겸
+2023***1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문*리
+2026***5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백*호
+2024***7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김*헌
+2026***0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이*석
+2026***0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장*호
+2026***0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설*훈
+2026***3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이*혁
+2026***2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김*환
 2026***4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박*영
+2026***2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박*현
+2026***1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KON** **RIYA
+2026***1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정*진
+2024***7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>함*현
+2026***8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이*민
+2026***2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정*
+2026***7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오*연
+2026***3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안*빈
+2026***2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이*민
+2026***9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>임*슬
+2026***3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정*현
+2025***3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박*민
+2026***9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정*원
+2026***3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장*주
+2026***9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최*원
+2023***0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YIN**NG
+2026***7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양*훈
+2026***8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>손*연
+2026***7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍*준
+2026***3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강*원
+2026***3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김*린
+2026***2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김*빈
+2026***3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조*준
+2026***1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이*희
+2026***7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고*록
+2021***9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황*민
+2019***1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박*우
+2026***0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김*오
+2024***9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이즈* *카코
+2026***1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -66,253 +296,38 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>김*규
-2026***6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김*유
-2023***9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>임*준
-2024***3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이*현
-2022***0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>안*율
-2026***3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>박*현
-2026***9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김*현
-2026***8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>권*원
-2026***2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김*빈
-2023***7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>홍*현
-2025***7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이*겸
+    <t>김*욱
+2024***0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이*영
+2026***7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박*몽
+2026***0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김*지
+2026***1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김*준
+2026***0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GE **O
 2023***1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>문*리
-2026***5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>백*호
-2024***7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김*헌
-2026***0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이*석
-2026***0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이*준
-2021***9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장*호
-2026***0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>설*훈
-2026***3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이*혁
-2026***2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김*환
-2026***4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>박*영
-2026***2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>박*현
-2026***1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KON** **RIYA
-2026***1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정*진
-2024***7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>함*현
-2026***8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이*민
-2026***2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정*
-2026***7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오*연
-2026***3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>안*빈
-2026***2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이*민
-2026***9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>임*슬
-2026***3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정*현
-2025***3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>박*민
-2026***9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정*원
-2026***3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장*주
-2026***9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>최*원
-2023***0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YIN**NG
-2026***7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>양*훈
-2026***8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>손*연
-2026***7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>홍*준
-2026***3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>강*원
-2026***3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김*린
-2026***2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김*빈
-2026***3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조*준
-2026***1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이*희
-2026***7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고*록
-2021***9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>황*민
-2019***1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>박*우
-2026***0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김*오
-2024***9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이즈* *카코
-2026***1</t>
+    <t>JU **XUN
+2025***0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -446,6 +461,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -454,9 +472,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -772,11 +787,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E92EEA4-D711-4770-AD4D-40CF77A5B207}">
-  <dimension ref="A2:M12"/>
+  <dimension ref="B2:N12"/>
   <sheetFormatPr defaultColWidth="17.8984375" defaultRowHeight="48" customHeight="1" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C2" s="2"/>
+    <row r="2" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -786,36 +800,34 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="2"/>
+    <row r="3" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="L3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M3" s="7"/>
+        <v>58</v>
+      </c>
+      <c r="M3" s="2"/>
+      <c r="N3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C4" s="1"/>
+    <row r="4" spans="2:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -825,68 +837,74 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="2" t="s">
+    </row>
+    <row r="6" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="6"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="I6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="5"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="5"/>
-      <c r="C7" s="1"/>
+    <row r="7" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="6"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -896,69 +914,67 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="5"/>
-      <c r="C8" s="3"/>
+    <row r="8" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="6"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="2" t="s">
+    </row>
+    <row r="9" spans="2:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="7"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="J9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="9" spans="1:13" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="6"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="1"/>
+    <row r="10" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -968,70 +984,75 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="2" t="s">
+    <row r="11" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="D11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="2" t="s">
+    </row>
+    <row r="12" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="D12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="B5:B9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/3학년 2학기/기인프/기인프 5반 좌석표 개선판.xlsx
+++ b/3학년 2학기/기인프/기인프 5반 좌석표 개선판.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\SOGANG\3학년 2학기\기인프\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E015F87-784C-4F0A-AEDF-5A7B77C37F7A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06415130-6790-4E82-863F-221043590087}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9564" xr2:uid="{127D69E5-7973-4135-B76A-078775FF16D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>교탁</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -311,11 +311,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>김*지
-2026***1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>김*준
 2026***0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -328,6 +323,16 @@
   <si>
     <t>JU **XUN
 2025***0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이*준
+2021***9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김*헌
+2026***9</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -806,11 +811,11 @@
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>1</v>
@@ -822,9 +827,11 @@
         <v>3</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="M3" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="N3" s="4"/>
     </row>
     <row r="4" spans="2:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -843,9 +850,7 @@
       <c r="B5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>55</v>
-      </c>
+      <c r="D5" s="2"/>
       <c r="E5" s="3"/>
       <c r="F5" s="2" t="s">
         <v>4</v>
@@ -863,7 +868,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>8</v>
@@ -920,7 +925,9 @@
       <c r="B8" s="6"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G8" s="2" t="s">
         <v>19</v>
       </c>
